--- a/grille_extract_test.xlsx
+++ b/grille_extract_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hodbert-e\Documents\GitHub\systematic_review_final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hodbere\Documents\GitHub\systematic_review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CA0C6D-BD15-4E06-98E0-653BA7EF8D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8FD43D-4C41-4C40-90FF-3858EA1DF5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26192" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -4358,7 +4355,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4441,10 +4438,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4708,7 +4701,18 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0A234209-000F-4083-8F59-7A4627BAD561}" name="Tableau1" displayName="Tableau1" ref="A1:BB105" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23">
-  <autoFilter ref="A1:BB105" xr:uid="{0A234209-000F-4083-8F59-7A4627BAD561}"/>
+  <autoFilter ref="A1:BB105" xr:uid="{0A234209-000F-4083-8F59-7A4627BAD561}">
+    <filterColumn colId="19">
+      <filters>
+        <filter val="Indirect"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="39">
+      <filters>
+        <filter val="yes"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BB105">
     <sortCondition ref="A1:A105"/>
   </sortState>
@@ -5036,54 +5040,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CM105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="4" width="11.375" customWidth="1"/>
+    <col min="1" max="1" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.109375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="19.5" style="6" customWidth="1"/>
-    <col min="7" max="7" width="40.375" style="6" customWidth="1"/>
-    <col min="8" max="8" width="31.375" style="13" customWidth="1"/>
-    <col min="9" max="12" width="31.375" style="6" customWidth="1"/>
-    <col min="13" max="13" width="31.375" style="14" customWidth="1"/>
-    <col min="14" max="14" width="44.25" style="7" customWidth="1"/>
-    <col min="15" max="15" width="40.375" customWidth="1"/>
-    <col min="16" max="18" width="32.75" customWidth="1"/>
-    <col min="19" max="19" width="27.25" style="18" customWidth="1"/>
-    <col min="20" max="20" width="27.25" customWidth="1"/>
-    <col min="21" max="21" width="54.625" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="40.33203125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="31.33203125" style="13" customWidth="1"/>
+    <col min="9" max="12" width="31.33203125" style="6" customWidth="1"/>
+    <col min="13" max="13" width="31.33203125" style="14" customWidth="1"/>
+    <col min="14" max="14" width="44.21875" style="7" customWidth="1"/>
+    <col min="15" max="15" width="40.33203125" customWidth="1"/>
+    <col min="16" max="18" width="32.77734375" customWidth="1"/>
+    <col min="19" max="19" width="27.21875" style="18" customWidth="1"/>
+    <col min="20" max="20" width="27.21875" customWidth="1"/>
+    <col min="21" max="21" width="54.6640625" customWidth="1"/>
     <col min="22" max="22" width="59" customWidth="1"/>
-    <col min="23" max="23" width="90.5" style="18" customWidth="1"/>
+    <col min="23" max="23" width="90.44140625" style="18" customWidth="1"/>
     <col min="24" max="24" width="31" customWidth="1"/>
-    <col min="25" max="25" width="26.5" style="15" customWidth="1"/>
-    <col min="26" max="26" width="26.5" customWidth="1"/>
-    <col min="27" max="27" width="41.25" customWidth="1"/>
+    <col min="25" max="25" width="26.44140625" style="15" customWidth="1"/>
+    <col min="26" max="26" width="26.44140625" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" customWidth="1"/>
     <col min="28" max="28" width="31" customWidth="1"/>
-    <col min="29" max="29" width="42.375" customWidth="1"/>
-    <col min="30" max="30" width="31.5" customWidth="1"/>
-    <col min="31" max="32" width="30.875" customWidth="1"/>
-    <col min="33" max="33" width="59.25" style="9" customWidth="1"/>
-    <col min="34" max="34" width="41.125" style="10" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="28.875" style="9" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="58.5" style="6" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="44.875" customWidth="1"/>
-    <col min="38" max="38" width="44.875" style="9" customWidth="1"/>
+    <col min="29" max="29" width="42.33203125" customWidth="1"/>
+    <col min="30" max="30" width="31.44140625" customWidth="1"/>
+    <col min="31" max="32" width="30.88671875" customWidth="1"/>
+    <col min="33" max="33" width="59.21875" style="9" customWidth="1"/>
+    <col min="34" max="34" width="41.109375" style="10" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="28.88671875" style="9" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="58.44140625" style="6" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="44.88671875" customWidth="1"/>
+    <col min="38" max="38" width="44.88671875" style="9" customWidth="1"/>
     <col min="39" max="39" width="28" style="10" customWidth="1"/>
-    <col min="40" max="40" width="20.5" customWidth="1"/>
-    <col min="41" max="41" width="22.25" customWidth="1"/>
-    <col min="42" max="42" width="31.125" customWidth="1"/>
+    <col min="40" max="40" width="20.44140625" customWidth="1"/>
+    <col min="41" max="41" width="22.21875" customWidth="1"/>
+    <col min="42" max="42" width="31.109375" customWidth="1"/>
     <col min="43" max="43" width="43" style="6" customWidth="1"/>
-    <col min="44" max="44" width="18.875" style="6" customWidth="1"/>
-    <col min="45" max="45" width="36.75" customWidth="1"/>
-    <col min="46" max="50" width="22.875" style="23" customWidth="1"/>
-    <col min="51" max="51" width="44.5" style="17" customWidth="1"/>
-    <col min="52" max="53" width="17.125" customWidth="1"/>
-    <col min="54" max="54" width="26.5" customWidth="1"/>
+    <col min="44" max="44" width="18.88671875" style="6" customWidth="1"/>
+    <col min="45" max="45" width="36.77734375" customWidth="1"/>
+    <col min="46" max="50" width="22.88671875" style="23" customWidth="1"/>
+    <col min="51" max="51" width="44.44140625" style="17" customWidth="1"/>
+    <col min="52" max="53" width="17.109375" customWidth="1"/>
+    <col min="54" max="54" width="26.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:91" s="3" customFormat="1" ht="51.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:91" s="3" customFormat="1" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>873</v>
       </c>
@@ -5247,7 +5251,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="2" spans="1:91" ht="39.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:91" ht="39.299999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>860</v>
       </c>
@@ -5380,7 +5384,7 @@
       <c r="AV2" t="s">
         <v>1123</v>
       </c>
-      <c r="AW2" s="40">
+      <c r="AW2" s="38">
         <v>45783</v>
       </c>
       <c r="AX2" t="s">
@@ -5389,17 +5393,17 @@
       <c r="AY2" t="s">
         <v>1049</v>
       </c>
-      <c r="AZ2" s="38" t="s">
+      <c r="AZ2" t="s">
         <v>1070</v>
       </c>
-      <c r="BA2" s="38" t="s">
+      <c r="BA2" t="s">
         <v>1071</v>
       </c>
-      <c r="BB2" s="38" t="s">
+      <c r="BB2" t="s">
         <v>1072</v>
       </c>
     </row>
-    <row r="3" spans="1:91" s="15" customFormat="1" ht="84.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:91" s="15" customFormat="1" ht="84.3" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1033</v>
       </c>
@@ -5534,7 +5538,7 @@
       <c r="AV3" t="s">
         <v>1123</v>
       </c>
-      <c r="AW3" s="40">
+      <c r="AW3" s="38">
         <v>45944</v>
       </c>
       <c r="AX3" t="s">
@@ -5584,7 +5588,7 @@
       <c r="CL3"/>
       <c r="CM3"/>
     </row>
-    <row r="4" spans="1:91" s="15" customFormat="1" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:91" s="15" customFormat="1" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1034</v>
       </c>
@@ -5719,7 +5723,7 @@
       <c r="AV4" t="s">
         <v>1123</v>
       </c>
-      <c r="AW4" s="40">
+      <c r="AW4" s="38">
         <v>45944</v>
       </c>
       <c r="AX4" t="s">
@@ -5769,7 +5773,7 @@
       <c r="CL4"/>
       <c r="CM4"/>
     </row>
-    <row r="5" spans="1:91" s="15" customFormat="1" ht="156.9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:91" s="15" customFormat="1" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>558</v>
       </c>
@@ -5908,7 +5912,7 @@
       <c r="AV5" t="s">
         <v>1123</v>
       </c>
-      <c r="AW5" s="40">
+      <c r="AW5" s="38">
         <v>45727</v>
       </c>
       <c r="AX5" t="s">
@@ -5964,7 +5968,7 @@
       <c r="CL5"/>
       <c r="CM5"/>
     </row>
-    <row r="6" spans="1:91" s="15" customFormat="1" ht="99.85" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:91" s="15" customFormat="1" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>796</v>
       </c>
@@ -6097,7 +6101,7 @@
       <c r="AV6" t="s">
         <v>1123</v>
       </c>
-      <c r="AW6" s="40">
+      <c r="AW6" s="38">
         <v>45782</v>
       </c>
       <c r="AX6" t="s">
@@ -6149,7 +6153,7 @@
       <c r="CL6"/>
       <c r="CM6"/>
     </row>
-    <row r="7" spans="1:91" s="15" customFormat="1" ht="128.4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:91" s="15" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>628</v>
       </c>
@@ -6284,7 +6288,7 @@
       <c r="AV7" t="s">
         <v>1123</v>
       </c>
-      <c r="AW7" s="40">
+      <c r="AW7" s="38">
         <v>45727</v>
       </c>
       <c r="AX7" t="s">
@@ -6293,13 +6297,13 @@
       <c r="AY7" t="s">
         <v>1049</v>
       </c>
-      <c r="AZ7" s="39" t="s">
+      <c r="AZ7" s="6" t="s">
         <v>637</v>
       </c>
-      <c r="BA7" s="39" t="s">
+      <c r="BA7" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="BB7" s="39" t="s">
+      <c r="BB7" s="6" t="s">
         <v>1073</v>
       </c>
       <c r="BC7"/>
@@ -6340,7 +6344,7 @@
       <c r="CL7"/>
       <c r="CM7"/>
     </row>
-    <row r="8" spans="1:91" s="15" customFormat="1" ht="103.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:91" s="15" customFormat="1" ht="103.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>453</v>
       </c>
@@ -6477,7 +6481,7 @@
       <c r="AV8" t="s">
         <v>1123</v>
       </c>
-      <c r="AW8" s="40">
+      <c r="AW8" s="38">
         <v>45715</v>
       </c>
       <c r="AX8" t="s">
@@ -6527,7 +6531,7 @@
       <c r="CL8"/>
       <c r="CM8"/>
     </row>
-    <row r="9" spans="1:91" ht="104.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:91" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>464</v>
       </c>
@@ -6670,7 +6674,7 @@
       <c r="AV9" t="s">
         <v>1123</v>
       </c>
-      <c r="AW9" s="40">
+      <c r="AW9" s="38">
         <v>45726</v>
       </c>
       <c r="AX9" t="s">
@@ -6679,17 +6683,17 @@
       <c r="AY9" t="s">
         <v>1049</v>
       </c>
-      <c r="AZ9" s="39" t="s">
+      <c r="AZ9" s="6" t="s">
         <v>1074</v>
       </c>
-      <c r="BA9" s="39" t="s">
+      <c r="BA9" s="6" t="s">
         <v>1075</v>
       </c>
-      <c r="BB9" s="39" t="s">
+      <c r="BB9" s="6" t="s">
         <v>1076</v>
       </c>
     </row>
-    <row r="10" spans="1:91" ht="199.7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:91" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>480</v>
       </c>
@@ -6832,7 +6836,7 @@
       <c r="AV10" t="s">
         <v>1123</v>
       </c>
-      <c r="AW10" s="40">
+      <c r="AW10" s="38">
         <v>45726</v>
       </c>
       <c r="AX10" t="s">
@@ -6844,14 +6848,14 @@
       <c r="AZ10" s="35" t="s">
         <v>493</v>
       </c>
-      <c r="BA10" s="39" t="s">
+      <c r="BA10" s="6" t="s">
         <v>1077</v>
       </c>
-      <c r="BB10" s="39" t="s">
+      <c r="BB10" s="6" t="s">
         <v>1078</v>
       </c>
     </row>
-    <row r="11" spans="1:91" ht="71.349999999999994" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:91" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>157</v>
       </c>
@@ -6987,7 +6991,7 @@
       <c r="AV11" t="s">
         <v>1123</v>
       </c>
-      <c r="AW11" s="40">
+      <c r="AW11" s="38">
         <v>45715</v>
       </c>
       <c r="AX11" t="s">
@@ -6996,17 +7000,17 @@
       <c r="AY11" t="s">
         <v>1049</v>
       </c>
-      <c r="AZ11" s="38" t="s">
+      <c r="AZ11" t="s">
         <v>1066</v>
       </c>
-      <c r="BA11" s="38" t="s">
+      <c r="BA11" t="s">
         <v>1067</v>
       </c>
-      <c r="BB11" s="38" t="s">
+      <c r="BB11" t="s">
         <v>1068</v>
       </c>
     </row>
-    <row r="12" spans="1:91" ht="57.1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:91" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>926</v>
       </c>
@@ -7130,7 +7134,7 @@
       <c r="BA12" s="12"/>
       <c r="BB12" s="12"/>
     </row>
-    <row r="13" spans="1:91" ht="57.1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:91" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>927</v>
       </c>
@@ -7254,7 +7258,7 @@
       <c r="BA13" s="12"/>
       <c r="BB13" s="12"/>
     </row>
-    <row r="14" spans="1:91" ht="57.1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:91" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>437</v>
       </c>
@@ -7392,7 +7396,7 @@
       <c r="AV14" t="s">
         <v>1123</v>
       </c>
-      <c r="AW14" s="40">
+      <c r="AW14" s="38">
         <v>45726</v>
       </c>
       <c r="AX14" t="s">
@@ -7411,7 +7415,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="15" spans="1:91" ht="85.6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:91" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>108</v>
       </c>
@@ -7552,7 +7556,7 @@
       <c r="AV15" t="s">
         <v>1123</v>
       </c>
-      <c r="AW15" s="40">
+      <c r="AW15" s="38">
         <v>45715</v>
       </c>
       <c r="AX15" t="s">
@@ -7571,7 +7575,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:91" ht="85.6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:91" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>580</v>
       </c>
@@ -7697,7 +7701,7 @@
       <c r="AV16" t="s">
         <v>1123</v>
       </c>
-      <c r="AW16" s="40">
+      <c r="AW16" s="38">
         <v>45715</v>
       </c>
       <c r="AX16" t="s">
@@ -7716,7 +7720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:54" ht="142.65" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:54" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>412</v>
       </c>
@@ -7854,7 +7858,7 @@
       <c r="AV17" t="s">
         <v>1123</v>
       </c>
-      <c r="AW17" s="40">
+      <c r="AW17" s="38">
         <v>45726</v>
       </c>
       <c r="AX17" t="s">
@@ -7863,17 +7867,17 @@
       <c r="AY17" t="s">
         <v>1049</v>
       </c>
-      <c r="AZ17" s="38" t="s">
+      <c r="AZ17" t="s">
         <v>422</v>
       </c>
-      <c r="BA17" s="38" t="s">
+      <c r="BA17" t="s">
         <v>423</v>
       </c>
-      <c r="BB17" s="38" t="s">
+      <c r="BB17" t="s">
         <v>1079</v>
       </c>
     </row>
-    <row r="18" spans="1:54" ht="57.1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:54" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>639</v>
       </c>
@@ -8014,7 +8018,7 @@
       <c r="AV18" t="s">
         <v>1123</v>
       </c>
-      <c r="AW18" s="40">
+      <c r="AW18" s="38">
         <v>45727</v>
       </c>
       <c r="AX18" t="s">
@@ -8033,7 +8037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:54" ht="99.85" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:54" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>361</v>
       </c>
@@ -8174,7 +8178,7 @@
       <c r="AV19" t="s">
         <v>1123</v>
       </c>
-      <c r="AW19" s="40">
+      <c r="AW19" s="38">
         <v>45725</v>
       </c>
       <c r="AX19" t="s">
@@ -8193,7 +8197,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="20" spans="1:54" ht="199.7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:54" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>309</v>
       </c>
@@ -8331,7 +8335,7 @@
       <c r="AV20" t="s">
         <v>1123</v>
       </c>
-      <c r="AW20" s="40">
+      <c r="AW20" s="38">
         <v>45721</v>
       </c>
       <c r="AX20" t="s">
@@ -8350,7 +8354,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="21" spans="1:54" ht="199.7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:54" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>932</v>
       </c>
@@ -8477,7 +8481,7 @@
       <c r="BA21" s="35"/>
       <c r="BB21" s="35"/>
     </row>
-    <row r="22" spans="1:54" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:54" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>933</v>
       </c>
@@ -8604,7 +8608,7 @@
       <c r="BA22" s="35"/>
       <c r="BB22" s="35"/>
     </row>
-    <row r="23" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:54" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>588</v>
       </c>
@@ -8735,7 +8739,7 @@
       <c r="AV23" t="s">
         <v>1123</v>
       </c>
-      <c r="AW23" s="40">
+      <c r="AW23" s="38">
         <v>45727</v>
       </c>
       <c r="AX23" t="s">
@@ -8754,7 +8758,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="1:54" ht="202.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:54" ht="202.2" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>325</v>
       </c>
@@ -8895,7 +8899,7 @@
       <c r="AV24" t="s">
         <v>1123</v>
       </c>
-      <c r="AW24" s="40">
+      <c r="AW24" s="38">
         <v>45721</v>
       </c>
       <c r="AX24" t="s">
@@ -8914,7 +8918,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="25" spans="1:54" ht="57.1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:54" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>601</v>
       </c>
@@ -9045,7 +9049,7 @@
       <c r="AV25" t="s">
         <v>1123</v>
       </c>
-      <c r="AW25" s="40">
+      <c r="AW25" s="38">
         <v>45727</v>
       </c>
       <c r="AX25" t="s">
@@ -9064,7 +9068,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="26" spans="1:54" ht="185.45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:54" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>0</v>
       </c>
@@ -9202,7 +9206,7 @@
       <c r="AV26" t="s">
         <v>1123</v>
       </c>
-      <c r="AW26" s="40">
+      <c r="AW26" s="38">
         <v>45715</v>
       </c>
       <c r="AX26" t="s">
@@ -9221,7 +9225,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:54" ht="129.1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:54" ht="165" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>538</v>
       </c>
@@ -9361,7 +9365,7 @@
       <c r="AV27" t="s">
         <v>1123</v>
       </c>
-      <c r="AW27" s="40">
+      <c r="AW27" s="38">
         <v>45727</v>
       </c>
       <c r="AX27" t="s">
@@ -9378,7 +9382,7 @@
       </c>
       <c r="BB27" s="36"/>
     </row>
-    <row r="28" spans="1:54" ht="142" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:54" ht="165" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>253</v>
       </c>
@@ -9519,7 +9523,7 @@
       <c r="AV28" t="s">
         <v>1123</v>
       </c>
-      <c r="AW28" s="40">
+      <c r="AW28" s="38">
         <v>45756</v>
       </c>
       <c r="AX28" t="s">
@@ -9538,7 +9542,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="29" spans="1:54" ht="115.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:54" ht="115.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>267</v>
       </c>
@@ -9679,7 +9683,7 @@
       <c r="AV29" t="s">
         <v>1123</v>
       </c>
-      <c r="AW29" s="40">
+      <c r="AW29" s="38">
         <v>45721</v>
       </c>
       <c r="AX29" t="s">
@@ -9698,7 +9702,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="30" spans="1:54" ht="99.85" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:54" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>279</v>
       </c>
@@ -9839,7 +9843,7 @@
       <c r="AV30" t="s">
         <v>1123</v>
       </c>
-      <c r="AW30" s="40">
+      <c r="AW30" s="38">
         <v>45721</v>
       </c>
       <c r="AX30" t="s">
@@ -9856,7 +9860,7 @@
       </c>
       <c r="BB30" s="12"/>
     </row>
-    <row r="31" spans="1:54" ht="85.6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:54" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>807</v>
       </c>
@@ -9997,7 +10001,7 @@
       <c r="AV31" t="s">
         <v>1123</v>
       </c>
-      <c r="AW31" s="40">
+      <c r="AW31" s="38">
         <v>45715</v>
       </c>
       <c r="AX31" t="s">
@@ -10016,7 +10020,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="32" spans="1:54" ht="103.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:54" ht="135" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>289</v>
       </c>
@@ -10157,7 +10161,7 @@
       <c r="AV32" t="s">
         <v>1123</v>
       </c>
-      <c r="AW32" s="40">
+      <c r="AW32" s="38">
         <v>45721</v>
       </c>
       <c r="AX32" t="s">
@@ -10176,7 +10180,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="33" spans="1:54" ht="85.6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:54" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>299</v>
       </c>
@@ -10317,7 +10321,7 @@
       <c r="AV33" t="s">
         <v>1123</v>
       </c>
-      <c r="AW33" s="40">
+      <c r="AW33" s="38">
         <v>45721</v>
       </c>
       <c r="AX33" t="s">
@@ -10336,7 +10340,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="34" spans="1:54" ht="99.85" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:54" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>1000</v>
       </c>
@@ -10460,7 +10464,7 @@
       <c r="AV34" t="s">
         <v>1123</v>
       </c>
-      <c r="AW34" s="40">
+      <c r="AW34" s="38">
         <v>45944</v>
       </c>
       <c r="AX34" t="s">
@@ -10473,7 +10477,7 @@
       <c r="BA34" s="36"/>
       <c r="BB34" s="36"/>
     </row>
-    <row r="35" spans="1:54" ht="85.6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:54" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>96</v>
       </c>
@@ -10613,7 +10617,7 @@
       <c r="AV35" t="s">
         <v>1123</v>
       </c>
-      <c r="AW35" s="40">
+      <c r="AW35" s="38">
         <v>45715</v>
       </c>
       <c r="AX35" t="s">
@@ -10632,7 +10636,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="1:54" ht="114.15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:54" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>845</v>
       </c>
@@ -10770,7 +10774,7 @@
       <c r="AV36" t="s">
         <v>1123</v>
       </c>
-      <c r="AW36" s="40">
+      <c r="AW36" s="38">
         <v>45727</v>
       </c>
       <c r="AX36" t="s">
@@ -10789,7 +10793,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="37" spans="1:54" ht="114.15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:54" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>209</v>
       </c>
@@ -10930,7 +10934,7 @@
       <c r="AV37" t="s">
         <v>1123</v>
       </c>
-      <c r="AW37" s="40">
+      <c r="AW37" s="38">
         <v>45715</v>
       </c>
       <c r="AX37" t="s">
@@ -10949,7 +10953,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="38" spans="1:54" ht="71.349999999999994" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:54" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>648</v>
       </c>
@@ -11090,7 +11094,7 @@
       <c r="AV38" t="s">
         <v>1123</v>
       </c>
-      <c r="AW38" s="40">
+      <c r="AW38" s="38">
         <v>45727</v>
       </c>
       <c r="AX38" t="s">
@@ -11109,7 +11113,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="39" spans="1:54" ht="142" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:54" ht="165" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>170</v>
       </c>
@@ -11247,7 +11251,7 @@
       <c r="AV39" t="s">
         <v>1123</v>
       </c>
-      <c r="AW39" s="40">
+      <c r="AW39" s="38">
         <v>45727</v>
       </c>
       <c r="AX39" t="s">
@@ -11266,7 +11270,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="40" spans="1:54" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:54" ht="100.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>928</v>
       </c>
@@ -11388,7 +11392,7 @@
       <c r="BA40" s="35"/>
       <c r="BB40" s="35"/>
     </row>
-    <row r="41" spans="1:54" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:54" ht="86.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>929</v>
       </c>
@@ -11510,7 +11514,7 @@
       <c r="BA41" s="35"/>
       <c r="BB41" s="35"/>
     </row>
-    <row r="42" spans="1:54" ht="73.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:54" ht="73.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>930</v>
       </c>
@@ -11632,7 +11636,7 @@
       <c r="BA42" s="35"/>
       <c r="BB42" s="35"/>
     </row>
-    <row r="43" spans="1:54" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:54" ht="115.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>657</v>
       </c>
@@ -11773,7 +11777,7 @@
       <c r="AV43" t="s">
         <v>1123</v>
       </c>
-      <c r="AW43" s="40">
+      <c r="AW43" s="38">
         <v>45727</v>
       </c>
       <c r="AX43" t="s">
@@ -11792,7 +11796,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="44" spans="1:54" ht="228.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:54" ht="230.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -11932,7 +11936,7 @@
       <c r="AV44" t="s">
         <v>1123</v>
       </c>
-      <c r="AW44" s="40">
+      <c r="AW44" s="38">
         <v>45715</v>
       </c>
       <c r="AX44" t="s">
@@ -11941,17 +11945,17 @@
       <c r="AY44" t="s">
         <v>1049</v>
       </c>
-      <c r="AZ44" s="38" t="s">
+      <c r="AZ44" t="s">
         <v>1120</v>
       </c>
-      <c r="BA44" s="38" t="s">
+      <c r="BA44" t="s">
         <v>1121</v>
       </c>
-      <c r="BB44" s="38" t="s">
+      <c r="BB44" t="s">
         <v>1122</v>
       </c>
     </row>
-    <row r="45" spans="1:54" ht="57.1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:54" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>1008</v>
       </c>
@@ -12028,7 +12032,7 @@
       <c r="AV45" t="s">
         <v>1123</v>
       </c>
-      <c r="AW45" s="40">
+      <c r="AW45" s="38">
         <v>45937</v>
       </c>
       <c r="AX45" t="s">
@@ -12041,7 +12045,7 @@
       <c r="BA45" s="21"/>
       <c r="BB45" s="21"/>
     </row>
-    <row r="46" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:54" ht="15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>1011</v>
       </c>
@@ -12163,7 +12167,7 @@
       <c r="BA46" s="21"/>
       <c r="BB46" s="21"/>
     </row>
-    <row r="47" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:54" ht="15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>1009</v>
       </c>
@@ -12285,7 +12289,7 @@
       <c r="BA47" s="21"/>
       <c r="BB47" s="21"/>
     </row>
-    <row r="48" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:54" ht="15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>1010</v>
       </c>
@@ -12407,7 +12411,7 @@
       <c r="BA48" s="21"/>
       <c r="BB48" s="21"/>
     </row>
-    <row r="49" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:54" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>665</v>
       </c>
@@ -12543,7 +12547,7 @@
       <c r="AV49" t="s">
         <v>1123</v>
       </c>
-      <c r="AW49" s="40">
+      <c r="AW49" s="38">
         <v>45727</v>
       </c>
       <c r="AX49" t="s">
@@ -12562,7 +12566,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="50" spans="1:54" ht="116.15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:54" ht="135" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>677</v>
       </c>
@@ -12703,7 +12707,7 @@
       <c r="AV50" t="s">
         <v>1123</v>
       </c>
-      <c r="AW50" s="40">
+      <c r="AW50" s="38">
         <v>45727</v>
       </c>
       <c r="AX50" t="s">
@@ -12722,7 +12726,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="51" spans="1:54" ht="71.349999999999994" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:54" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>687</v>
       </c>
@@ -12853,7 +12857,7 @@
       <c r="AV51" t="s">
         <v>1123</v>
       </c>
-      <c r="AW51" s="40">
+      <c r="AW51" s="38">
         <v>45727</v>
       </c>
       <c r="AX51" t="s">
@@ -12872,7 +12876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:54" ht="114.15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:54" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>695</v>
       </c>
@@ -13015,7 +13019,7 @@
       <c r="AV52" t="s">
         <v>1123</v>
       </c>
-      <c r="AW52" s="40">
+      <c r="AW52" s="38">
         <v>45727</v>
       </c>
       <c r="AX52" t="s">
@@ -13024,17 +13028,17 @@
       <c r="AY52" t="s">
         <v>1058</v>
       </c>
-      <c r="AZ52" s="39" t="s">
+      <c r="AZ52" s="6" t="s">
         <v>1080</v>
       </c>
-      <c r="BA52" s="39" t="s">
+      <c r="BA52" s="6" t="s">
         <v>1081</v>
       </c>
-      <c r="BB52" s="39" t="s">
+      <c r="BB52" s="6" t="s">
         <v>1082</v>
       </c>
     </row>
-    <row r="53" spans="1:54" ht="90.35" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:54" ht="105" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>704</v>
       </c>
@@ -13175,7 +13179,7 @@
       <c r="AV53" t="s">
         <v>1123</v>
       </c>
-      <c r="AW53" s="40">
+      <c r="AW53" s="38">
         <v>45727</v>
       </c>
       <c r="AX53" t="s">
@@ -13194,7 +13198,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="54" spans="1:54" ht="156.9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:54" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>712</v>
       </c>
@@ -13335,7 +13339,7 @@
       <c r="AV54" t="s">
         <v>1123</v>
       </c>
-      <c r="AW54" s="40">
+      <c r="AW54" s="38">
         <v>45727</v>
       </c>
       <c r="AX54" t="s">
@@ -13347,14 +13351,14 @@
       <c r="AZ54" s="35" t="s">
         <v>721</v>
       </c>
-      <c r="BA54" s="39" t="s">
+      <c r="BA54" s="6" t="s">
         <v>1083</v>
       </c>
-      <c r="BB54" s="39" t="s">
+      <c r="BB54" s="6" t="s">
         <v>1084</v>
       </c>
     </row>
-    <row r="55" spans="1:54" ht="129.1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:54" ht="150" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>722</v>
       </c>
@@ -13488,7 +13492,7 @@
       <c r="AV55" t="s">
         <v>1123</v>
       </c>
-      <c r="AW55" s="40">
+      <c r="AW55" s="38">
         <v>45727</v>
       </c>
       <c r="AX55" t="s">
@@ -13503,11 +13507,11 @@
       <c r="BA55" s="35" t="s">
         <v>730</v>
       </c>
-      <c r="BB55" s="39" t="s">
+      <c r="BB55" s="6" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="56" spans="1:54" ht="185.45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:54" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>732</v>
       </c>
@@ -13648,7 +13652,7 @@
       <c r="AV56" t="s">
         <v>1123</v>
       </c>
-      <c r="AW56" s="40">
+      <c r="AW56" s="38">
         <v>45727</v>
       </c>
       <c r="AX56" t="s">
@@ -13657,17 +13661,17 @@
       <c r="AY56" t="s">
         <v>1052</v>
       </c>
-      <c r="AZ56" s="39" t="s">
+      <c r="AZ56" s="6" t="s">
         <v>1085</v>
       </c>
-      <c r="BA56" s="39" t="s">
+      <c r="BA56" s="6" t="s">
         <v>1086</v>
       </c>
-      <c r="BB56" s="39" t="s">
+      <c r="BB56" s="6" t="s">
         <v>1087</v>
       </c>
     </row>
-    <row r="57" spans="1:54" ht="242.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:54" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>739</v>
       </c>
@@ -13808,7 +13812,7 @@
       <c r="AV57" t="s">
         <v>1123</v>
       </c>
-      <c r="AW57" s="40">
+      <c r="AW57" s="38">
         <v>45727</v>
       </c>
       <c r="AX57" t="s">
@@ -13820,14 +13824,14 @@
       <c r="AZ57" s="35" t="s">
         <v>746</v>
       </c>
-      <c r="BA57" s="39" t="s">
+      <c r="BA57" s="6" t="s">
         <v>1088</v>
       </c>
       <c r="BB57" s="35">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:54" ht="99.85" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:54" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>424</v>
       </c>
@@ -13962,7 +13966,7 @@
       <c r="AV58" t="s">
         <v>1123</v>
       </c>
-      <c r="AW58" s="40">
+      <c r="AW58" s="38">
         <v>45726</v>
       </c>
       <c r="AX58" t="s">
@@ -13971,17 +13975,17 @@
       <c r="AY58" t="s">
         <v>1054</v>
       </c>
-      <c r="AZ58" s="38" t="s">
+      <c r="AZ58" t="s">
         <v>434</v>
       </c>
-      <c r="BA58" s="38" t="s">
+      <c r="BA58" t="s">
         <v>435</v>
       </c>
-      <c r="BB58" s="38" t="s">
+      <c r="BB58" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="59" spans="1:54" ht="57.1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:54" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>40</v>
       </c>
@@ -14114,7 +14118,7 @@
       <c r="AV59" t="s">
         <v>1123</v>
       </c>
-      <c r="AW59" s="40">
+      <c r="AW59" s="38">
         <v>45715</v>
       </c>
       <c r="AX59" t="s">
@@ -14123,17 +14127,17 @@
       <c r="AY59" t="s">
         <v>1049</v>
       </c>
-      <c r="AZ59" s="38" t="s">
+      <c r="AZ59" t="s">
         <v>1117</v>
       </c>
-      <c r="BA59" s="38" t="s">
+      <c r="BA59" t="s">
         <v>1118</v>
       </c>
-      <c r="BB59" s="38" t="s">
+      <c r="BB59" t="s">
         <v>1119</v>
       </c>
     </row>
-    <row r="60" spans="1:54" ht="133.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:54" ht="133.80000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>765</v>
       </c>
@@ -14268,7 +14272,7 @@
       <c r="AV60" t="s">
         <v>1123</v>
       </c>
-      <c r="AW60" s="40">
+      <c r="AW60" s="38">
         <v>45770</v>
       </c>
       <c r="AX60" t="s">
@@ -14287,7 +14291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:54" ht="114.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:54" ht="114.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>50</v>
       </c>
@@ -14424,7 +14428,7 @@
       <c r="AV61" t="s">
         <v>1123</v>
       </c>
-      <c r="AW61" s="40">
+      <c r="AW61" s="38">
         <v>45715</v>
       </c>
       <c r="AX61" t="s">
@@ -14433,17 +14437,17 @@
       <c r="AY61" t="s">
         <v>1059</v>
       </c>
-      <c r="AZ61" s="38" t="s">
+      <c r="AZ61" t="s">
         <v>1114</v>
       </c>
-      <c r="BA61" s="38" t="s">
+      <c r="BA61" t="s">
         <v>1115</v>
       </c>
-      <c r="BB61" s="38" t="s">
+      <c r="BB61" t="s">
         <v>1116</v>
       </c>
     </row>
-    <row r="62" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:54" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -14578,7 +14582,7 @@
       <c r="AV62" t="s">
         <v>1123</v>
       </c>
-      <c r="AW62" s="40">
+      <c r="AW62" s="38">
         <v>45715</v>
       </c>
       <c r="AX62" t="s">
@@ -14587,17 +14591,17 @@
       <c r="AY62" t="s">
         <v>1055</v>
       </c>
-      <c r="AZ62" s="38" t="s">
+      <c r="AZ62" t="s">
         <v>1111</v>
       </c>
-      <c r="BA62" s="38" t="s">
+      <c r="BA62" t="s">
         <v>1112</v>
       </c>
-      <c r="BB62" s="38" t="s">
+      <c r="BB62" t="s">
         <v>1113</v>
       </c>
     </row>
-    <row r="63" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:54" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -14732,7 +14736,7 @@
       <c r="AV63" t="s">
         <v>1123</v>
       </c>
-      <c r="AW63" s="40">
+      <c r="AW63" s="38">
         <v>45715</v>
       </c>
       <c r="AX63" t="s">
@@ -14741,17 +14745,17 @@
       <c r="AY63" s="9" t="s">
         <v>1055</v>
       </c>
-      <c r="AZ63" s="38" t="s">
+      <c r="AZ63" t="s">
         <v>1108</v>
       </c>
-      <c r="BA63" s="38" t="s">
+      <c r="BA63" t="s">
         <v>1109</v>
       </c>
-      <c r="BB63" s="38" t="s">
+      <c r="BB63" t="s">
         <v>1110</v>
       </c>
     </row>
-    <row r="64" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:54" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>73</v>
       </c>
@@ -14888,7 +14892,7 @@
       <c r="AV64" t="s">
         <v>1123</v>
       </c>
-      <c r="AW64" s="40">
+      <c r="AW64" s="38">
         <v>45715</v>
       </c>
       <c r="AX64" t="s">
@@ -14897,17 +14901,17 @@
       <c r="AY64" s="9" t="s">
         <v>1055</v>
       </c>
-      <c r="AZ64" s="38" t="s">
+      <c r="AZ64" t="s">
         <v>1105</v>
       </c>
-      <c r="BA64" s="38" t="s">
+      <c r="BA64" t="s">
         <v>1106</v>
       </c>
-      <c r="BB64" s="38" t="s">
+      <c r="BB64" t="s">
         <v>1107</v>
       </c>
     </row>
-    <row r="65" spans="1:54" ht="28.55" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:54" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>1026</v>
       </c>
@@ -15021,7 +15025,7 @@
       <c r="AV65" t="s">
         <v>1123</v>
       </c>
-      <c r="AW65" s="40">
+      <c r="AW65" s="38">
         <v>45944</v>
       </c>
       <c r="AX65" t="s">
@@ -15034,7 +15038,7 @@
       <c r="BA65" s="21"/>
       <c r="BB65" s="21"/>
     </row>
-    <row r="66" spans="1:54" ht="71.349999999999994" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:54" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>337</v>
       </c>
@@ -15165,7 +15169,7 @@
       <c r="AV66" t="s">
         <v>1123</v>
       </c>
-      <c r="AW66" s="40">
+      <c r="AW66" s="38">
         <v>45721</v>
       </c>
       <c r="AX66" t="s">
@@ -15174,17 +15178,17 @@
       <c r="AY66" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AZ66" s="38" t="s">
+      <c r="AZ66" t="s">
         <v>346</v>
       </c>
-      <c r="BA66" s="38" t="s">
+      <c r="BA66" t="s">
         <v>347</v>
       </c>
-      <c r="BB66" s="38" t="s">
+      <c r="BB66" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="67" spans="1:54" ht="71.349999999999994" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:54" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>349</v>
       </c>
@@ -15319,7 +15323,7 @@
       <c r="AV67" t="s">
         <v>1123</v>
       </c>
-      <c r="AW67" s="40">
+      <c r="AW67" s="38">
         <v>45725</v>
       </c>
       <c r="AX67" t="s">
@@ -15338,7 +15342,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="68" spans="1:54" ht="85.6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:54" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>1021</v>
       </c>
@@ -15471,7 +15475,7 @@
       <c r="AV68" t="s">
         <v>1123</v>
       </c>
-      <c r="AW68" s="40">
+      <c r="AW68" s="38">
         <v>45944</v>
       </c>
       <c r="AX68" t="s">
@@ -15484,7 +15488,7 @@
       <c r="BA68" s="21"/>
       <c r="BB68" s="21"/>
     </row>
-    <row r="69" spans="1:54" ht="142.65" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:54" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>237</v>
       </c>
@@ -15622,7 +15626,7 @@
       <c r="AV69" t="s">
         <v>1123</v>
       </c>
-      <c r="AW69" s="40">
+      <c r="AW69" s="38">
         <v>45727</v>
       </c>
       <c r="AX69" t="s">
@@ -15641,7 +15645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:54" ht="99.85" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:54" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>222</v>
       </c>
@@ -15774,7 +15778,7 @@
       <c r="AV70" t="s">
         <v>1123</v>
       </c>
-      <c r="AW70" s="40">
+      <c r="AW70" s="38">
         <v>45715</v>
       </c>
       <c r="AX70" t="s">
@@ -15783,17 +15787,17 @@
       <c r="AY70" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AZ70" s="38" t="s">
+      <c r="AZ70" t="s">
         <v>1089</v>
       </c>
-      <c r="BA70" s="38" t="s">
+      <c r="BA70" t="s">
         <v>1090</v>
       </c>
-      <c r="BB70" s="38" t="s">
+      <c r="BB70" t="s">
         <v>1091</v>
       </c>
     </row>
-    <row r="71" spans="1:54" ht="90.35" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:54" ht="105" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>504</v>
       </c>
@@ -15934,7 +15938,7 @@
       <c r="AV71" t="s">
         <v>1123</v>
       </c>
-      <c r="AW71" s="40">
+      <c r="AW71" s="38">
         <v>45726</v>
       </c>
       <c r="AX71" t="s">
@@ -15953,7 +15957,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="72" spans="1:54" ht="120.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:54" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>935</v>
       </c>
@@ -16082,7 +16086,7 @@
       <c r="BA72" s="35"/>
       <c r="BB72" s="35"/>
     </row>
-    <row r="73" spans="1:54" ht="85.6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:54" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>936</v>
       </c>
@@ -16211,7 +16215,7 @@
       <c r="BA73" s="35"/>
       <c r="BB73" s="35"/>
     </row>
-    <row r="74" spans="1:54" ht="116.15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:54" ht="135" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>494</v>
       </c>
@@ -16352,7 +16356,7 @@
       <c r="AV74" t="s">
         <v>1123</v>
       </c>
-      <c r="AW74" s="40">
+      <c r="AW74" s="38">
         <v>45726</v>
       </c>
       <c r="AX74" t="s">
@@ -16371,7 +16375,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="75" spans="1:54" ht="193.6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:54" ht="240" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>776</v>
       </c>
@@ -16509,7 +16513,7 @@
       <c r="AV75" t="s">
         <v>1123</v>
       </c>
-      <c r="AW75" s="40">
+      <c r="AW75" s="38">
         <v>45727</v>
       </c>
       <c r="AX75" t="s">
@@ -16528,7 +16532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:54" ht="28.55" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:54" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>615</v>
       </c>
@@ -16669,7 +16673,7 @@
       <c r="AV76" t="s">
         <v>1123</v>
       </c>
-      <c r="AW76" s="40">
+      <c r="AW76" s="38">
         <v>45770</v>
       </c>
       <c r="AX76" t="s">
@@ -16688,7 +16692,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="77" spans="1:54" ht="28.55" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:54" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>938</v>
       </c>
@@ -16816,7 +16820,7 @@
       <c r="BA77" s="12"/>
       <c r="BB77" s="12"/>
     </row>
-    <row r="78" spans="1:54" ht="28.55" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:54" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>937</v>
       </c>
@@ -16944,7 +16948,7 @@
       <c r="BA78" s="12"/>
       <c r="BB78" s="12"/>
     </row>
-    <row r="79" spans="1:54" ht="85.6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:54" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>387</v>
       </c>
@@ -17082,7 +17086,7 @@
       <c r="AV79" t="s">
         <v>1123</v>
       </c>
-      <c r="AW79" s="40">
+      <c r="AW79" s="38">
         <v>45722</v>
       </c>
       <c r="AX79" t="s">
@@ -17091,17 +17095,17 @@
       <c r="AY79" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AZ79" s="38" t="s">
+      <c r="AZ79" t="s">
         <v>398</v>
       </c>
-      <c r="BA79" s="38" t="s">
+      <c r="BA79" t="s">
         <v>399</v>
       </c>
-      <c r="BB79" s="38" t="s">
+      <c r="BB79" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="80" spans="1:54" ht="71.349999999999994" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:54" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>401</v>
       </c>
@@ -17239,7 +17243,7 @@
       <c r="AV80" t="s">
         <v>1123</v>
       </c>
-      <c r="AW80" s="40">
+      <c r="AW80" s="38">
         <v>45722</v>
       </c>
       <c r="AX80" t="s">
@@ -17248,17 +17252,17 @@
       <c r="AY80" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AZ80" s="38" t="s">
+      <c r="AZ80" t="s">
         <v>409</v>
       </c>
-      <c r="BA80" s="38" t="s">
+      <c r="BA80" t="s">
         <v>410</v>
       </c>
-      <c r="BB80" s="38" t="s">
+      <c r="BB80" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="81" spans="1:54" ht="57.1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:54" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>189</v>
       </c>
@@ -17390,7 +17394,7 @@
       <c r="AV81" t="s">
         <v>1123</v>
       </c>
-      <c r="AW81" s="40">
+      <c r="AW81" s="38">
         <v>45714</v>
       </c>
       <c r="AX81" t="s">
@@ -17409,7 +17413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:54" ht="57.1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:54" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>199</v>
       </c>
@@ -17544,7 +17548,7 @@
       <c r="AV82" t="s">
         <v>1123</v>
       </c>
-      <c r="AW82" s="40">
+      <c r="AW82" s="38">
         <v>45714</v>
       </c>
       <c r="AX82" t="s">
@@ -17563,7 +17567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:54" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:54" ht="46.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>747</v>
       </c>
@@ -17699,7 +17703,7 @@
       <c r="AV83" t="s">
         <v>1123</v>
       </c>
-      <c r="AW83" s="40">
+      <c r="AW83" s="38">
         <v>45724</v>
       </c>
       <c r="AX83" t="s">
@@ -17708,17 +17712,17 @@
       <c r="AY83" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AZ83" s="39" t="s">
+      <c r="AZ83" s="6" t="s">
         <v>1092</v>
       </c>
-      <c r="BA83" s="39" t="s">
+      <c r="BA83" s="6" t="s">
         <v>1093</v>
       </c>
-      <c r="BB83" s="39" t="s">
+      <c r="BB83" s="6" t="s">
         <v>1094</v>
       </c>
     </row>
-    <row r="84" spans="1:54" ht="81.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:54" ht="81.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>570</v>
       </c>
@@ -17859,7 +17863,7 @@
       <c r="AV84" t="s">
         <v>1123</v>
       </c>
-      <c r="AW84" s="40">
+      <c r="AW84" s="38">
         <v>45723</v>
       </c>
       <c r="AX84" t="s">
@@ -17868,17 +17872,17 @@
       <c r="AY84" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AZ84" s="38" t="s">
+      <c r="AZ84" t="s">
         <v>1095</v>
       </c>
-      <c r="BA84" s="38" t="s">
+      <c r="BA84" t="s">
         <v>1096</v>
       </c>
-      <c r="BB84" s="38" t="s">
+      <c r="BB84" t="s">
         <v>1097</v>
       </c>
     </row>
-    <row r="85" spans="1:54" ht="156.9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:54" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>828</v>
       </c>
@@ -18012,7 +18016,7 @@
       <c r="AV85" t="s">
         <v>1123</v>
       </c>
-      <c r="AW85" s="40">
+      <c r="AW85" s="38">
         <v>45723</v>
       </c>
       <c r="AX85" t="s">
@@ -18031,7 +18035,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="86" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:54" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>951</v>
       </c>
@@ -18157,7 +18161,7 @@
       <c r="BA86" s="35"/>
       <c r="BB86" s="35"/>
     </row>
-    <row r="87" spans="1:54" ht="157.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:54" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>953</v>
       </c>
@@ -18283,7 +18287,7 @@
       <c r="BA87" s="35"/>
       <c r="BB87" s="35"/>
     </row>
-    <row r="88" spans="1:54" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:54" ht="43.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>952</v>
       </c>
@@ -18411,7 +18415,7 @@
       <c r="BA88" s="35"/>
       <c r="BB88" s="35"/>
     </row>
-    <row r="89" spans="1:54" ht="149.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:54" ht="150" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>950</v>
       </c>
@@ -18537,7 +18541,7 @@
       <c r="BA89" s="35"/>
       <c r="BB89" s="35"/>
     </row>
-    <row r="90" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:54" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>949</v>
       </c>
@@ -18663,7 +18667,7 @@
       <c r="BA90" s="35"/>
       <c r="BB90" s="35"/>
     </row>
-    <row r="91" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:54" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>372</v>
       </c>
@@ -18804,7 +18808,7 @@
       <c r="AV91" t="s">
         <v>1123</v>
       </c>
-      <c r="AW91" s="40">
+      <c r="AW91" s="38">
         <v>45722</v>
       </c>
       <c r="AX91" t="s">
@@ -18813,17 +18817,17 @@
       <c r="AY91" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="AZ91" s="38" t="s">
+      <c r="AZ91" t="s">
         <v>384</v>
       </c>
-      <c r="BA91" s="38" t="s">
+      <c r="BA91" t="s">
         <v>385</v>
       </c>
-      <c r="BB91" s="38" t="s">
+      <c r="BB91" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="92" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:54" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>524</v>
       </c>
@@ -18961,7 +18965,7 @@
       <c r="AV92" t="s">
         <v>1123</v>
       </c>
-      <c r="AW92" s="40">
+      <c r="AW92" s="38">
         <v>45723</v>
       </c>
       <c r="AX92" t="s">
@@ -18980,7 +18984,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="93" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>785</v>
       </c>
@@ -19118,7 +19122,7 @@
       <c r="AV93" t="s">
         <v>1123</v>
       </c>
-      <c r="AW93" s="40">
+      <c r="AW93" s="38">
         <v>45723</v>
       </c>
       <c r="AX93" t="s">
@@ -19137,7 +19141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:54" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>549</v>
       </c>
@@ -19274,7 +19278,7 @@
       <c r="AV94" t="s">
         <v>1123</v>
       </c>
-      <c r="AW94" s="40">
+      <c r="AW94" s="38">
         <v>45723</v>
       </c>
       <c r="AX94" t="s">
@@ -19287,7 +19291,7 @@
       <c r="BA94" s="35"/>
       <c r="BB94" s="35"/>
     </row>
-    <row r="95" spans="1:54" ht="72.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:54" ht="72.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>755</v>
       </c>
@@ -19425,7 +19429,7 @@
       <c r="AV95" t="s">
         <v>1123</v>
       </c>
-      <c r="AW95" s="40">
+      <c r="AW95" s="38">
         <v>45728</v>
       </c>
       <c r="AX95" t="s">
@@ -19440,11 +19444,11 @@
       <c r="BA95" s="12" t="s">
         <v>764</v>
       </c>
-      <c r="BB95" s="38" t="s">
+      <c r="BB95" t="s">
         <v>1098</v>
       </c>
     </row>
-    <row r="96" spans="1:54" ht="129.1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:54" ht="150" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>818</v>
       </c>
@@ -19579,7 +19583,7 @@
       <c r="AV96" t="s">
         <v>1123</v>
       </c>
-      <c r="AW96" s="40">
+      <c r="AW96" s="38">
         <v>45728</v>
       </c>
       <c r="AX96" t="s">
@@ -19598,7 +19602,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="97" spans="1:54" ht="35.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:54" ht="35.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>85</v>
       </c>
@@ -19733,7 +19737,7 @@
       <c r="AV97" t="s">
         <v>1123</v>
       </c>
-      <c r="AW97" s="40">
+      <c r="AW97" s="38">
         <v>45728</v>
       </c>
       <c r="AX97" t="s">
@@ -19742,15 +19746,15 @@
       <c r="AY97" s="9" t="s">
         <v>1055</v>
       </c>
-      <c r="AZ97" s="38" t="s">
+      <c r="AZ97" t="s">
         <v>1103</v>
       </c>
-      <c r="BA97" s="38" t="s">
+      <c r="BA97" t="s">
         <v>1104</v>
       </c>
       <c r="BB97" s="21"/>
     </row>
-    <row r="98" spans="1:54" ht="142" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:54" ht="165" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>126</v>
       </c>
@@ -19890,7 +19894,7 @@
       <c r="AV98" t="s">
         <v>1123</v>
       </c>
-      <c r="AW98" s="40">
+      <c r="AW98" s="38">
         <v>45728</v>
       </c>
       <c r="AX98" t="s">
@@ -19909,7 +19913,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="99" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:54" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>921</v>
       </c>
@@ -20037,7 +20041,7 @@
       <c r="BA99" s="35"/>
       <c r="BB99" s="35"/>
     </row>
-    <row r="100" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:54" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>922</v>
       </c>
@@ -20165,7 +20169,7 @@
       <c r="BA100" s="35"/>
       <c r="BB100" s="35"/>
     </row>
-    <row r="101" spans="1:54" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:54" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>954</v>
       </c>
@@ -20293,7 +20297,7 @@
       <c r="BA101" s="35"/>
       <c r="BB101" s="35"/>
     </row>
-    <row r="102" spans="1:54" ht="71.349999999999994" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:54" ht="90" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>146</v>
       </c>
@@ -20433,7 +20437,7 @@
       <c r="AV102" t="s">
         <v>1123</v>
       </c>
-      <c r="AW102" s="40">
+      <c r="AW102" s="38">
         <v>45728</v>
       </c>
       <c r="AX102" t="s">
@@ -20452,7 +20456,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="103" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:54" ht="15" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>923</v>
       </c>
@@ -20580,7 +20584,7 @@
       <c r="BA103" s="35"/>
       <c r="BB103" s="35"/>
     </row>
-    <row r="104" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:54" ht="15" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>924</v>
       </c>
@@ -20708,7 +20712,7 @@
       <c r="BA104" s="35"/>
       <c r="BB104" s="35"/>
     </row>
-    <row r="105" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:54" ht="15" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>925</v>
       </c>
